--- a/artfynd/A 22974-2022 artfynd.xlsx
+++ b/artfynd/A 22974-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22974-2022 artfynd.xlsx
+++ b/artfynd/A 22974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86876430</v>
+        <v>99822276</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408870.8592588378</v>
+        <v>408883</v>
       </c>
       <c r="R2" t="n">
-        <v>7024726.629012525</v>
+        <v>7024815</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101621114</v>
+        <v>101621101</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,13 +823,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408900.1664518212</v>
+        <v>408861</v>
       </c>
       <c r="R3" t="n">
-        <v>7024934.734123913</v>
+        <v>7024744</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,19 +856,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,12 +889,7 @@
         <v>101621123</v>
       </c>
       <c r="B4" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408900.1664518212</v>
+        <v>408900</v>
       </c>
       <c r="R4" t="n">
-        <v>7024934.734123913</v>
+        <v>7024935</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,19 +958,9 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,6 +985,218 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86876430</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>408871</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7024727</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101621114</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>408900</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7024935</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22974-2022 artfynd.xlsx
+++ b/artfynd/A 22974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99822276</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86876430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621114</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>